--- a/examples/by_plot_type/spatial_roi/data.xlsx
+++ b/examples/by_plot_type/spatial_roi/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,10 +470,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1770.05</v>
+        <v>929.09</v>
       </c>
       <c r="D2" t="n">
-        <v>1050</v>
+        <v>550.75</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -496,10 +496,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1784.39</v>
+        <v>940.39</v>
       </c>
       <c r="D3" t="n">
-        <v>1206.91</v>
+        <v>643.08</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -522,10 +522,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1730.44</v>
+        <v>905.72</v>
       </c>
       <c r="D4" t="n">
-        <v>1358.76</v>
+        <v>729.67</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -548,10 +548,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>1606.56</v>
+        <v>850.47</v>
       </c>
       <c r="D5" t="n">
-        <v>1461.5</v>
+        <v>805.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -574,10 +574,10 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>1468.82</v>
+        <v>757.85</v>
       </c>
       <c r="D6" t="n">
-        <v>1529.14</v>
+        <v>831.39</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>1318.1</v>
+        <v>673.73</v>
       </c>
       <c r="D7" t="n">
-        <v>1523.68</v>
+        <v>841.51</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -626,10 +626,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>1183.23</v>
+        <v>595.8200000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>1514.37</v>
+        <v>849.67</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -652,10 +652,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>1036.23</v>
+        <v>517.08</v>
       </c>
       <c r="D9" t="n">
-        <v>1518.08</v>
+        <v>844.61</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -678,10 +678,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>889.75</v>
+        <v>430.31</v>
       </c>
       <c r="D10" t="n">
-        <v>1465.75</v>
+        <v>837.42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -704,10 +704,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>768.87</v>
+        <v>344.47</v>
       </c>
       <c r="D11" t="n">
-        <v>1359.2</v>
+        <v>802.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>714.72</v>
+        <v>273.83</v>
       </c>
       <c r="D12" t="n">
-        <v>1207.17</v>
+        <v>736.65</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -756,10 +756,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>731.95</v>
+        <v>252.45</v>
       </c>
       <c r="D13" t="n">
-        <v>1050</v>
+        <v>642.75</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -782,10 +782,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>797.9</v>
+        <v>268.88</v>
       </c>
       <c r="D14" t="n">
-        <v>917.25</v>
+        <v>550.75</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -808,10 +808,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>866.83</v>
+        <v>296.37</v>
       </c>
       <c r="D15" t="n">
-        <v>803.75</v>
+        <v>470.51</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -834,10 +834,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>925.99</v>
+        <v>342.17</v>
       </c>
       <c r="D16" t="n">
-        <v>676.0700000000001</v>
+        <v>404.31</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -860,10 +860,10 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>1028.52</v>
+        <v>375.78</v>
       </c>
       <c r="D17" t="n">
-        <v>565.03</v>
+        <v>330.71</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -886,10 +886,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>1168.29</v>
+        <v>430.66</v>
       </c>
       <c r="D18" t="n">
-        <v>481.7</v>
+        <v>264.68</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -912,10 +912,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>1329.75</v>
+        <v>503.86</v>
       </c>
       <c r="D19" t="n">
-        <v>495.34</v>
+        <v>207.54</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -938,10 +938,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>1468.54</v>
+        <v>595.8200000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>571.46</v>
+        <v>196.56</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -964,10 +964,10 @@
         <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>1576.08</v>
+        <v>684.38</v>
       </c>
       <c r="D21" t="n">
-        <v>673.6799999999999</v>
+        <v>220.22</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -990,10 +990,10 @@
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>1642.21</v>
+        <v>757.1</v>
       </c>
       <c r="D22" t="n">
-        <v>797.9400000000001</v>
+        <v>271.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -1016,10 +1016,10 @@
         <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>1717.63</v>
+        <v>818.77</v>
       </c>
       <c r="D23" t="n">
-        <v>912.6900000000001</v>
+        <v>327.79</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1028,59 +1028,59 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tumor core</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ROI_2</t>
+          <t>ROI_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>2310.17</v>
+        <v>848.11</v>
       </c>
       <c r="D24" t="n">
-        <v>1500</v>
+        <v>405.09</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ROI_2</t>
+          <t>ROI_1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ROI_2</t>
+          <t>ROI_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>2329.48</v>
+        <v>895.54</v>
       </c>
       <c r="D25" t="n">
-        <v>1602.62</v>
+        <v>470.44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ROI_2</t>
+          <t>ROI_1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Tumour region</t>
         </is>
       </c>
     </row>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2288.24</v>
+        <v>1433.31</v>
       </c>
       <c r="D26" t="n">
-        <v>1698.09</v>
+        <v>850.75</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>2209.12</v>
+        <v>1443.81</v>
       </c>
       <c r="D27" t="n">
-        <v>1764.41</v>
+        <v>922.5599999999999</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>2114.87</v>
+        <v>1423.35</v>
       </c>
       <c r="D28" t="n">
-        <v>1795.32</v>
+        <v>993.66</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>2022.5</v>
+        <v>1377.2</v>
       </c>
       <c r="D29" t="n">
-        <v>1795.59</v>
+        <v>1052.13</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>1938.47</v>
+        <v>1306.96</v>
       </c>
       <c r="D30" t="n">
-        <v>1788.88</v>
+        <v>1077.89</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>1846.03</v>
+        <v>1238.74</v>
       </c>
       <c r="D31" t="n">
-        <v>1793.35</v>
+        <v>1085.58</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1247,13 +1247,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>1745.92</v>
+        <v>1175.82</v>
       </c>
       <c r="D32" t="n">
-        <v>1770.14</v>
+        <v>1089.81</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>1684.45</v>
+        <v>1113.92</v>
       </c>
       <c r="D33" t="n">
-        <v>1689.94</v>
+        <v>1081.75</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C34" t="n">
-        <v>1637.21</v>
+        <v>1043.74</v>
       </c>
       <c r="D34" t="n">
-        <v>1600.65</v>
+        <v>1079.52</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>1657.6</v>
+        <v>976.49</v>
       </c>
       <c r="D35" t="n">
-        <v>1500</v>
+        <v>1050.08</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>1687.41</v>
+        <v>925.13</v>
       </c>
       <c r="D36" t="n">
-        <v>1414.09</v>
+        <v>995.48</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C37" t="n">
-        <v>1729.53</v>
+        <v>907.5</v>
       </c>
       <c r="D37" t="n">
-        <v>1339.04</v>
+        <v>922.64</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>1773.16</v>
+        <v>917.52</v>
       </c>
       <c r="D38" t="n">
-        <v>1261.29</v>
+        <v>850.75</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C39" t="n">
-        <v>1838.62</v>
+        <v>945.71</v>
       </c>
       <c r="D39" t="n">
-        <v>1190.42</v>
+        <v>789.09</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C40" t="n">
-        <v>1927.8</v>
+        <v>975.89</v>
       </c>
       <c r="D40" t="n">
-        <v>1136.92</v>
+        <v>735.3200000000001</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" t="n">
-        <v>2032.06</v>
+        <v>1007.5</v>
       </c>
       <c r="D41" t="n">
-        <v>1137.93</v>
+        <v>682.4299999999999</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>2120.54</v>
+        <v>1045.1</v>
       </c>
       <c r="D42" t="n">
-        <v>1192.25</v>
+        <v>624.34</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C43" t="n">
-        <v>2187.97</v>
+        <v>1104</v>
       </c>
       <c r="D43" t="n">
-        <v>1259.99</v>
+        <v>582.71</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1559,13 +1559,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C44" t="n">
-        <v>2228.83</v>
+        <v>1175.82</v>
       </c>
       <c r="D44" t="n">
-        <v>1340.09</v>
+        <v>563.0700000000001</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C45" t="n">
-        <v>2270.4</v>
+        <v>1248.36</v>
       </c>
       <c r="D45" t="n">
-        <v>1414.73</v>
+        <v>580.01</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1600,111 +1600,111 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Invasive front</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ROI_3</t>
+          <t>ROI_2</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>1194.58</v>
+        <v>1303.75</v>
       </c>
       <c r="D46" t="n">
-        <v>1750</v>
+        <v>629.16</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ROI_3</t>
+          <t>ROI_2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ROI_3</t>
+          <t>ROI_2</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C47" t="n">
-        <v>1215.27</v>
+        <v>1343.66</v>
       </c>
       <c r="D47" t="n">
-        <v>1842.57</v>
+        <v>682.91</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ROI_3</t>
+          <t>ROI_2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ROI_3</t>
+          <t>ROI_2</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C48" t="n">
-        <v>1176.22</v>
+        <v>1377.7</v>
       </c>
       <c r="D48" t="n">
-        <v>1927.52</v>
+        <v>734.1900000000001</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ROI_3</t>
+          <t>ROI_2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ROI_3</t>
+          <t>ROI_2</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C49" t="n">
-        <v>1099.94</v>
+        <v>1406.28</v>
       </c>
       <c r="D49" t="n">
-        <v>1980.75</v>
+        <v>789</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ROI_3</t>
+          <t>ROI_2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Immune-rich region</t>
         </is>
       </c>
     </row>
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>1022.13</v>
+        <v>942.91</v>
       </c>
       <c r="D50" t="n">
-        <v>2017.42</v>
+        <v>1090.75</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>938.53</v>
+        <v>958.75</v>
       </c>
       <c r="D51" t="n">
-        <v>2018</v>
+        <v>1153.16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -1767,13 +1767,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>861.38</v>
+        <v>931.01</v>
       </c>
       <c r="D52" t="n">
-        <v>2018.61</v>
+        <v>1209.22</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>779.3200000000001</v>
+        <v>897.1</v>
       </c>
       <c r="D53" t="n">
-        <v>2014.24</v>
+        <v>1262.03</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>693.91</v>
+        <v>836.3</v>
       </c>
       <c r="D54" t="n">
-        <v>1987.84</v>
+        <v>1282.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C55" t="n">
-        <v>612.3200000000001</v>
+        <v>779.5700000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>1934.88</v>
+        <v>1291.37</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C56" t="n">
-        <v>583.22</v>
+        <v>725.8200000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>1843.02</v>
+        <v>1291.61</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C57" t="n">
-        <v>596.85</v>
+        <v>672.38</v>
       </c>
       <c r="D57" t="n">
-        <v>1750</v>
+        <v>1290.19</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -1923,13 +1923,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C58" t="n">
-        <v>632.86</v>
+        <v>613.08</v>
       </c>
       <c r="D58" t="n">
-        <v>1671.56</v>
+        <v>1286.02</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C59" t="n">
-        <v>668.33</v>
+        <v>561.78</v>
       </c>
       <c r="D59" t="n">
-        <v>1601.12</v>
+        <v>1254.79</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C60" t="n">
-        <v>713.45</v>
+        <v>516.6900000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>1534.7</v>
+        <v>1211.49</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C61" t="n">
-        <v>770.34</v>
+        <v>501.01</v>
       </c>
       <c r="D61" t="n">
-        <v>1466.08</v>
+        <v>1150.99</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C62" t="n">
-        <v>853.0599999999999</v>
+        <v>511.42</v>
       </c>
       <c r="D62" t="n">
-        <v>1423.56</v>
+        <v>1090.75</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C63" t="n">
-        <v>946.66</v>
+        <v>530.45</v>
       </c>
       <c r="D63" t="n">
-        <v>1425.47</v>
+        <v>1038.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C64" t="n">
-        <v>1029.89</v>
+        <v>548.99</v>
       </c>
       <c r="D64" t="n">
-        <v>1465.57</v>
+        <v>988.66</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C65" t="n">
-        <v>1084.6</v>
+        <v>581.66</v>
       </c>
       <c r="D65" t="n">
-        <v>1536.96</v>
+        <v>946.59</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>1127.62</v>
+        <v>612.55</v>
       </c>
       <c r="D66" t="n">
-        <v>1603.72</v>
+        <v>894.55</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Immune aggregate</t>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
@@ -2157,22 +2157,178 @@
         </is>
       </c>
       <c r="B67" t="n">
+        <v>17</v>
+      </c>
+      <c r="C67" t="n">
+        <v>663.0700000000001</v>
+      </c>
+      <c r="D67" t="n">
+        <v>856.5700000000001</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Stromal region</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>18</v>
+      </c>
+      <c r="C68" t="n">
+        <v>725.8200000000001</v>
+      </c>
+      <c r="D68" t="n">
+        <v>838.87</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Stromal region</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>19</v>
+      </c>
+      <c r="C69" t="n">
+        <v>788.41</v>
+      </c>
+      <c r="D69" t="n">
+        <v>857.15</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Stromal region</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>20</v>
+      </c>
+      <c r="C70" t="n">
+        <v>839.71</v>
+      </c>
+      <c r="D70" t="n">
+        <v>893.48</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Stromal region</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
         <v>21</v>
       </c>
-      <c r="C67" t="n">
-        <v>1161.86</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1673.11</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>ROI_3</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Immune aggregate</t>
+      <c r="C71" t="n">
+        <v>871.14</v>
+      </c>
+      <c r="D71" t="n">
+        <v>945.4299999999999</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Stromal region</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>22</v>
+      </c>
+      <c r="C72" t="n">
+        <v>897.9400000000001</v>
+      </c>
+      <c r="D72" t="n">
+        <v>991.37</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Stromal region</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>23</v>
+      </c>
+      <c r="C73" t="n">
+        <v>924.24</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1037.58</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ROI_3</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Stromal region</t>
         </is>
       </c>
     </row>
